--- a/synthetic/documents/xlsx/order_039_TIT-PO-01038.xlsx
+++ b/synthetic/documents/xlsx/order_039_TIT-PO-01038.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Titan Industrial Supply Co. (SYNTHETIC)</t>
+          <t>Omega Manufacturing Inc. (SYNTHETIC)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20-Mar-2026</t>
+          <t>01-Jul-2026</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Titan East Branch</t>
+          <t>Omega Shipping Location 2</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TIS-MIS-3045</t>
+          <t>ADH-SGG-011</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Utility Knife retractable</t>
+          <t>Super Glue Gel (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -567,14 +567,14 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.66</v>
+        <v>25.28</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>56.6</v>
+        <v>252.8</v>
       </c>
     </row>
     <row r="10">
@@ -583,56 +583,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TIS-ABR-3795</t>
+          <t>TLS-UTK-163</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Cut-off Wheel 4.5x.045x7/8 220 grit</t>
+          <t>Utility Knife Retractable (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>37.98</v>
+        <v>9.92</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>455.76</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>TIS-PPE-2658</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Nitrile Work Gloves industrial Orange size XL</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>DZN</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>337.35</v>
+        <v>49.6</v>
       </c>
     </row>
   </sheetData>

--- a/synthetic/documents/xlsx/order_039_TIT-PO-01038.xlsx
+++ b/synthetic/documents/xlsx/order_039_TIT-PO-01038.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01-Jul-2026</t>
+          <t>23-Jun-2026</t>
         </is>
       </c>
     </row>
@@ -507,103 +507,173 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Omega Shipping Location 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+          <t>Omega Shipping Location 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Date:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ADH-SGG-011</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Super Glue Gel (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>252.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>TLS-AWR-6IN</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Adjustable Wrench 6in (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>59.76</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>TLS-UTK-163</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Utility Knife Retractable (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>FST-HNT-34-10</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Hex 3/4-10 Grade 5 Zinc (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>49.6</v>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>104.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>JAN-DSP-258</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Disinfectant Spray (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>133.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>OMEGA-JAN-4074</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Paper Towel Roll 1P Natural (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>642.12</v>
       </c>
     </row>
   </sheetData>
